--- a/data/P2/P2T1_BQ1.xlsx
+++ b/data/P2/P2T1_BQ1.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DB425A-91D9-2147-A82E-1B2AB0C9DAF0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388FCD04-95F0-A341-8CF1-25B4A5685628}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="31200" yWindow="4780" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -205,13 +206,56 @@
   </si>
   <si>
     <t>不同</t>
+  </si>
+  <si>
+    <t>All animals can breathe and move, but they're different in many amazing ways.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Birds lay eggs with hard shells. They want to keep their baby birds safe.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fish scales help keep them safe from dangerous fish that want to bite them.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amphibians need to have wet skin, so they live in wet places.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Whales are water mammals, and cats, rabbits, and lions are land mammals.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有動物都會呼吸和移動，但牠們在許多奇妙的方面各不相同。</t>
+  </si>
+  <si>
+    <t>鳥類產下有堅硬外殼的蛋，牠們要保護雛鳥安全。</t>
+  </si>
+  <si>
+    <t>魚鱗幫助保護牠們，免於被想咬牠們的危險魚類攻擊。</t>
+  </si>
+  <si>
+    <t>兩棲動物需要保持皮膚濕潤，所以牠們住在潮濕的地方。</t>
+  </si>
+  <si>
+    <t>鯨魚是水中哺乳動物，而貓、兔子和獅子是陸地哺乳動物。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -239,6 +283,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -262,7 +321,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -270,6 +329,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -912,4 +977,68 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0B94A8-B1C1-7A4E-83B6-FEE43E2C368E}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="93.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:12" ht="18">
+      <c r="A2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18">
+      <c r="A3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18">
+      <c r="A4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18">
+      <c r="A5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18">
+      <c r="A6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/P2/P2T1_BQ1.xlsx
+++ b/data/P2/P2T1_BQ1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388FCD04-95F0-A341-8CF1-25B4A5685628}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C42678D-DDE8-D241-9496-E35D7AAAAB5C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="4780" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="31200" yWindow="4780" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="110">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -249,13 +249,130 @@
   </si>
   <si>
     <t>鯨魚是水中哺乳動物，而貓、兔子和獅子是陸地哺乳動物。</t>
+  </si>
+  <si>
+    <t>phonetics</t>
+  </si>
+  <si>
+    <t>syllable</t>
+  </si>
+  <si>
+    <t>/ˈænɪmlz/</t>
+  </si>
+  <si>
+    <t>an-i-mals</t>
+  </si>
+  <si>
+    <t>/ˈmæmlz/</t>
+  </si>
+  <si>
+    <t>mam-mals</t>
+  </si>
+  <si>
+    <t>/æmˈfɪbiənz/</t>
+  </si>
+  <si>
+    <t>am-phib-i-ans</t>
+  </si>
+  <si>
+    <t>/wɪŋz/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/ˈfeðəz/</t>
+  </si>
+  <si>
+    <t>fea-thers</t>
+  </si>
+  <si>
+    <t>/fɜː(r)/</t>
+  </si>
+  <si>
+    <t>/ɡɪlz/</t>
+  </si>
+  <si>
+    <t>/skeɪlz/</t>
+  </si>
+  <si>
+    <t>/fɪnz/</t>
+  </si>
+  <si>
+    <t>/teɪl/</t>
+  </si>
+  <si>
+    <t>/skɪn/</t>
+  </si>
+  <si>
+    <t>/klɔː/</t>
+  </si>
+  <si>
+    <t>/biːk/</t>
+  </si>
+  <si>
+    <t>/pek/</t>
+  </si>
+  <si>
+    <t>/briːð/</t>
+  </si>
+  <si>
+    <t>/skwɔːk/</t>
+  </si>
+  <si>
+    <t>/faɪt/</t>
+  </si>
+  <si>
+    <t>/hʌnt/</t>
+  </si>
+  <si>
+    <t>/kriːp/</t>
+  </si>
+  <si>
+    <t>/ɪˈskeɪp/</t>
+  </si>
+  <si>
+    <t>es-cape</t>
+  </si>
+  <si>
+    <t>/strɒŋ/</t>
+  </si>
+  <si>
+    <t>/ˈdʒentl/</t>
+  </si>
+  <si>
+    <t>gen-tle</t>
+  </si>
+  <si>
+    <t>/smɑːt/</t>
+  </si>
+  <si>
+    <t>/kɑːm/</t>
+  </si>
+  <si>
+    <t>/ˈpeɪʃnt/</t>
+  </si>
+  <si>
+    <t>pa-tient</t>
+  </si>
+  <si>
+    <t>/fɪəs/</t>
+  </si>
+  <si>
+    <t>/seɪm/</t>
+  </si>
+  <si>
+    <t>/ˈdɪfrənt/</t>
+  </si>
+  <si>
+    <t>dif-fer-ent</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -298,6 +415,14 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -307,12 +432,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -321,7 +461,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -335,6 +475,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -651,10 +797,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -664,8 +810,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -675,8 +827,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -686,8 +844,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -697,8 +861,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -708,8 +878,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -719,8 +895,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -730,8 +912,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -741,8 +929,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -752,8 +946,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -763,8 +963,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -774,8 +980,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -785,8 +997,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -796,8 +1014,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -807,8 +1031,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
@@ -818,8 +1048,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -829,8 +1065,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -840,8 +1082,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -851,8 +1099,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -862,8 +1116,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
@@ -873,8 +1133,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
@@ -884,8 +1150,14 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
@@ -895,8 +1167,14 @@
       <c r="C22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -906,8 +1184,14 @@
       <c r="C23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
@@ -917,8 +1201,14 @@
       <c r="C24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -928,8 +1218,14 @@
       <c r="C25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -939,8 +1235,14 @@
       <c r="C26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
@@ -950,8 +1252,14 @@
       <c r="C27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
@@ -961,8 +1269,14 @@
       <c r="C28">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
@@ -971,6 +1285,12 @@
       </c>
       <c r="C29">
         <v>6</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/P2/P2T1_BQ1.xlsx
+++ b/data/P2/P2T1_BQ1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C42678D-DDE8-D241-9496-E35D7AAAAB5C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407360E8-1E39-6D46-81B8-78F8792C3D1B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="4780" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="29200" yWindow="1000" windowWidth="29440" windowHeight="19420" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="139">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -366,6 +366,93 @@
   </si>
   <si>
     <t>dif-fer-ent</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+  </si>
+  <si>
+    <t>All living creatures like birds, dogs and frogs</t>
+  </si>
+  <si>
+    <t>Animals with fur, drink mom’s milk when young</t>
+  </si>
+  <si>
+    <t>Animals live in water and on land, like frogs</t>
+  </si>
+  <si>
+    <t>Body parts for birds to fly in the sky</t>
+  </si>
+  <si>
+    <t>Soft light covering on birds’ bodies</t>
+  </si>
+  <si>
+    <t>Thick soft hair on cats, dogs and bears</t>
+  </si>
+  <si>
+    <t>Parts fish use to get air under water</t>
+  </si>
+  <si>
+    <t>Hard thin small pieces covering fish skin</t>
+  </si>
+  <si>
+    <t>Flat parts on fish to swim in water</t>
+  </si>
+  <si>
+    <t>Long part at the back of many animals</t>
+  </si>
+  <si>
+    <t>Outer soft cover of animal bodies</t>
+  </si>
+  <si>
+    <t>Sharp hard nail on animal feet</t>
+  </si>
+  <si>
+    <t>Hard mouth part of birds</t>
+  </si>
+  <si>
+    <t>Birds hit things quickly with their beaks</t>
+  </si>
+  <si>
+    <t>Take air into body and let it out</t>
+  </si>
+  <si>
+    <t>Loud noisy sound from birds</t>
+  </si>
+  <si>
+    <t>Hit or push another animal</t>
+  </si>
+  <si>
+    <t>Look and catch other small animals for food</t>
+  </si>
+  <si>
+    <t>Move slowly and quietly close to something</t>
+  </si>
+  <si>
+    <t>Run away to stay safe</t>
+  </si>
+  <si>
+    <t>Have big power, can lift heavy things</t>
+  </si>
+  <si>
+    <t>Soft and careful, will not hurt others</t>
+  </si>
+  <si>
+    <t>Quick to learn new things</t>
+  </si>
+  <si>
+    <t>Quiet and not excited or angry</t>
+  </si>
+  <si>
+    <t>Can wait slowly without getting mad</t>
+  </si>
+  <si>
+    <t>Wild and ready to fight, scary</t>
+  </si>
+  <si>
+    <t>Look or act just like each other</t>
+  </si>
+  <si>
+    <t>Not look or act like each other</t>
   </si>
 </sst>
 </file>
@@ -797,10 +884,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="6" max="6" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -816,8 +907,13 @@
       <c r="E1" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -833,8 +929,11 @@
       <c r="E2" s="6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -850,8 +949,11 @@
       <c r="E3" s="6" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -867,8 +969,11 @@
       <c r="E4" s="6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -884,8 +989,11 @@
       <c r="E5" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -901,8 +1009,11 @@
       <c r="E6" s="6" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -918,8 +1029,11 @@
       <c r="E7" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -935,8 +1049,11 @@
       <c r="E8" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -952,8 +1069,11 @@
       <c r="E9" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -969,8 +1089,11 @@
       <c r="E10" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -986,8 +1109,11 @@
       <c r="E11" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -1003,8 +1129,11 @@
       <c r="E12" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -1020,8 +1149,11 @@
       <c r="E13" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
@@ -1037,8 +1169,11 @@
       <c r="E14" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
         <v>16</v>
       </c>
@@ -1054,8 +1189,11 @@
       <c r="E15" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
         <v>17</v>
       </c>
@@ -1071,8 +1209,11 @@
       <c r="E16" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -1088,8 +1229,11 @@
       <c r="E17" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
@@ -1105,8 +1249,11 @@
       <c r="E18" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -1122,8 +1269,11 @@
       <c r="E19" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
@@ -1139,8 +1289,11 @@
       <c r="E20" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
@@ -1156,8 +1309,11 @@
       <c r="E21" s="6" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
@@ -1173,8 +1329,11 @@
       <c r="E22" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -1190,8 +1349,11 @@
       <c r="E23" s="6" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
@@ -1207,8 +1369,11 @@
       <c r="E24" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -1224,8 +1389,11 @@
       <c r="E25" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -1241,8 +1409,11 @@
       <c r="E26" s="6" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
@@ -1258,8 +1429,11 @@
       <c r="E27" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
@@ -1275,8 +1449,11 @@
       <c r="E28" s="6" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
@@ -1291,6 +1468,9 @@
       </c>
       <c r="E29" s="6" t="s">
         <v>109</v>
+      </c>
+      <c r="F29" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
